--- a/data/results/main_cases/shapley_ieee14_exact_results.xlsx
+++ b/data/results/main_cases/shapley_ieee14_exact_results.xlsx
@@ -5140,19 +5140,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01607876378412828</v>
+        <v>0.009334585053193461</v>
       </c>
       <c r="C2" t="n">
-        <v>8.74072836792087</v>
+        <v>5.074461785287168</v>
       </c>
       <c r="D2" t="n">
-        <v>2.431468906666221</v>
+        <v>1.411598156313215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998707418437821</v>
+        <v>0.9999565227865108</v>
       </c>
       <c r="F2" t="n">
-        <v>7.291018004008206</v>
+        <v>4.273346780577807</v>
       </c>
     </row>
   </sheetData>
